--- a/Results/Study 1/ResNet18/Confusion Matrices.xlsx
+++ b/Results/Study 1/ResNet18/Confusion Matrices.xlsx
@@ -400,10 +400,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>417</v>
+        <v>382</v>
       </c>
       <c r="C2">
-        <v>223</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="C3">
-        <v>516</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
@@ -440,10 +440,10 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C2">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -451,10 +451,10 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
